--- a/public/exports-from-60-with-coowners/11931316.xlsx
+++ b/public/exports-from-60-with-coowners/11931316.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/11931316.xlsx
+++ b/public/exports-from-60-with-coowners/11931316.xlsx
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 45</t>
+          <t xml:space="preserve">Vejlebrovej 57</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J150">
-        <v>11924</v>
+        <v>650</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11306,25 +11306,25 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>364</v>
+        <v>11924</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931691</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 47</t>
+          <t xml:space="preserve">Vejlebrovej 45</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11381,25 +11381,25 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J152">
-        <v>940</v>
+        <v>364</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931691</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 57</t>
+          <t xml:space="preserve">Vejlebrovej 47</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11456,25 +11456,25 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J153">
-        <v>650</v>
+        <v>940</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931692</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
